--- a/orange_part/emails_output/emails.xlsx
+++ b/orange_part/emails_output/emails.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RIRI\Desktop\orange api\PFE_Email_Analysis\orange_part\emails_output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71163A03-791F-470C-B0F6-68168AEC9B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>UID</t>
   </si>
@@ -31,8 +25,32 @@
     <t>Attachments</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>Yessine Ht &lt;yessineht@gmail.com&gt;
-Bonjour,_x000D_
+Bonjour,_x005F_x000D_
+_x005F_x000D_
+Je vous écris afin de vous demander l’autorisation de prendre un congé._x005F_x000D_
+_x005F_x000D_
+Durant cette période, je veillerai à ce que toutes mes tâches en cours_x005F_x000D_
+soient organisées ou transmises afin d’assurer la continuité du travail._x005F_x000D_
+_x005F_x000D_
+Je reste bien entendu disponible pour toute information complémentaire et_x005F_x000D_
+je vous remercie par avance pour votre compréhension._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb_x005F_x000D_
+developpeur</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Demande de congé 
+ Date: Wed, 22 Apr 2026 13:50:06 +0100 
+ Bonjour,_x000D_
 _x000D_
 Je vous écris afin de vous demander l’autorisation de prendre un congé._x000D_
 _x000D_
@@ -47,25 +65,37 @@
 developpeur</t>
   </si>
   <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: problème de connexion 
+ Date: Thu, 7 May 2026 10:59:54 +0100 
+ Bonjour,_x000D_
+Je rencontre actuellement un problème lors de l’accès à mon espace client._x000D_
+En effet, l’application affiche une erreur 404, ce qui m’empêche d’y_x000D_
+accéder. Je ne comprends pas l’origine de ce problème et je vous serais_x000D_
+reconnaissant de bien vouloir m’aider à le résoudre dans les plus brefs_x000D_
+délais. Je reste à votre disposition pour toute information complémentaire._x000D_
+Cordialement,_x000D_
+yessine Haj Taieb_x000D_
+[image: image.png]</t>
+  </si>
+  <si>
     <t>Doctor_Note_with_Signature.pdf</t>
+  </si>
+  <si>
+    <t>image.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -84,44 +114,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -409,33 +413,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/orange_part/emails_output/emails.xlsx
+++ b/orange_part/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>UID</t>
   </si>
@@ -25,10 +25,7 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>31</t>
   </si>
   <si>
     <t>Yessine Ht &lt;yessineht@gmail.com&gt;
@@ -50,39 +47,84 @@
     <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
  Subject: Demande de congé 
  Date: Wed, 22 Apr 2026 13:50:06 +0100 
- Bonjour,_x000D_
-_x000D_
-Je vous écris afin de vous demander l’autorisation de prendre un congé._x000D_
-_x000D_
-Durant cette période, je veillerai à ce que toutes mes tâches en cours_x000D_
-soient organisées ou transmises afin d’assurer la continuité du travail._x000D_
-_x000D_
-Je reste bien entendu disponible pour toute information complémentaire et_x000D_
-je vous remercie par avance pour votre compréhension._x000D_
-_x000D_
-Cordialement,_x000D_
-yessine haj taieb_x000D_
+ Bonjour,_x005F_x000D_
+_x005F_x000D_
+Je vous écris afin de vous demander l’autorisation de prendre un congé._x005F_x000D_
+_x005F_x000D_
+Durant cette période, je veillerai à ce que toutes mes tâches en cours_x005F_x000D_
+soient organisées ou transmises afin d’assurer la continuité du travail._x005F_x000D_
+_x005F_x000D_
+Je reste bien entendu disponible pour toute information complémentaire et_x005F_x000D_
+je vous remercie par avance pour votre compréhension._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb_x005F_x000D_
 developpeur</t>
   </si>
   <si>
     <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
  Subject: problème de connexion 
  Date: Thu, 7 May 2026 10:59:54 +0100 
- Bonjour,_x000D_
-Je rencontre actuellement un problème lors de l’accès à mon espace client._x000D_
-En effet, l’application affiche une erreur 404, ce qui m’empêche d’y_x000D_
-accéder. Je ne comprends pas l’origine de ce problème et je vous serais_x000D_
-reconnaissant de bien vouloir m’aider à le résoudre dans les plus brefs_x000D_
-délais. Je reste à votre disposition pour toute information complémentaire._x000D_
+ Bonjour,_x005F_x000D_
+Je rencontre actuellement un problème lors de l’accès à mon espace client._x005F_x000D_
+En effet, l’application affiche une erreur 404, ce qui m’empêche d’y_x005F_x000D_
+accéder. Je ne comprends pas l’origine de ce problème et je vous serais_x005F_x000D_
+reconnaissant de bien vouloir m’aider à le résoudre dans les plus brefs_x005F_x000D_
+délais. Je reste à votre disposition pour toute information complémentaire._x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine Haj Taieb_x005F_x000D_
+[image: image.png]</t>
+  </si>
+  <si>
+    <t>From: Mail Delivery Subsystem &lt;mailer-daemon@googlemail.com&gt; 
+ Subject: Delivery Status Notification (Delay) 
+ Date: Mon, 11 May 2026 08:13:37 -0700 (PDT) 
+ _x005F_x000D_
+** Delivery incomplete **_x005F_x000D_
+_x005F_x000D_
+There was a temporary problem delivering your message to recla@admin.com. Gmail will retry for 44 more hours. You'll be notified if the delivery fails permanently._x005F_x000D_
+_x005F_x000D_
+Learn more here: https://support.google.com/mail/answer/7720_x005F_x000D_
+_x005F_x000D_
+The response was:_x005F_x000D_
+_x005F_x000D_
+The recipient server did not accept our requests to connect. For more information, go to https://support.google.com/mail/answer/7720 _x005F_x000D_
+[localhost.admin.com. 127.0.0.1: timed out]</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Yessine Ht &lt;yessineht@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Mission Order Request/*MailSub*/ 
+ Date: Tue, 19 May 2026 21:42:45 +0100 
+ J'espère que vous allez bien ! Je me permets de vous contacter afin de_x000D_
+solliciter votre validation pour un court déplacement professionnel prévu_x000D_
+les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x000D_
+activités en cours qui nécessitent vraiment une présence sur place, et je_x000D_
+souhaite m'assurer que tout se passe dans les meilleures conditions._x000D_
+_x000D_
+Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x000D_
+pouvez me joindre à l'adresse yessineht@gmail.com, et la destination est_x000D_
+Kairouan pour ces deux journées. L'accord de mon responsable est encore en_x000D_
+attente, mais je souhaitais vous transmettre cette demande en avance afin_x000D_
+d'éviter tout délai de traitement._x000D_
+_x000D_
+Si vous avez besoin de quoi que ce soit de ma part — documents_x000D_
+supplémentaires, détails sur les objectifs de la mission, ou autre —_x000D_
+n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x000D_
+plus brefs délais._x000D_
+_x000D_
+Merci beaucoup pour votre aide et votre disponibilité !_x000D_
+_x000D_
 Cordialement,_x000D_
-yessine Haj Taieb_x000D_
-[image: image.png]</t>
+yessine haj taieb</t>
   </si>
   <si>
     <t>Doctor_Note_with_Signature.pdf</t>
   </si>
   <si>
     <t>image.png</t>
+  </si>
+  <si>
+    <t>icon.png</t>
   </si>
 </sst>
 </file>
@@ -414,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -433,29 +475,48 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
+      <c r="A3">
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
+      <c r="A4">
+        <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/orange_part/emails_output/emails.xlsx
+++ b/orange_part/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>UID</t>
   </si>
@@ -25,7 +25,10 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>31</t>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>Yessine Ht &lt;yessineht@gmail.com&gt;
@@ -95,27 +98,264 @@
     <t>From: /*MailSender*/Yessine Ht &lt;yessineht@gmail.com&gt;/*MailSender*/ 
  Subject: /*MailSub*/Mission Order Request/*MailSub*/ 
  Date: Tue, 19 May 2026 21:42:45 +0100 
- J'espère que vous allez bien ! Je me permets de vous contacter afin de_x000D_
-solliciter votre validation pour un court déplacement professionnel prévu_x000D_
-les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x000D_
-activités en cours qui nécessitent vraiment une présence sur place, et je_x000D_
-souhaite m'assurer que tout se passe dans les meilleures conditions._x000D_
-_x000D_
-Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x000D_
-pouvez me joindre à l'adresse yessineht@gmail.com, et la destination est_x000D_
-Kairouan pour ces deux journées. L'accord de mon responsable est encore en_x000D_
-attente, mais je souhaitais vous transmettre cette demande en avance afin_x000D_
-d'éviter tout délai de traitement._x000D_
-_x000D_
-Si vous avez besoin de quoi que ce soit de ma part — documents_x000D_
-supplémentaires, détails sur les objectifs de la mission, ou autre —_x000D_
-n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x000D_
-plus brefs délais._x000D_
-_x000D_
-Merci beaucoup pour votre aide et votre disponibilité !_x000D_
+ J'espère que vous allez bien ! Je me permets de vous contacter afin de_x005F_x000D_
+solliciter votre validation pour un court déplacement professionnel prévu_x005F_x000D_
+les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x005F_x000D_
+activités en cours qui nécessitent vraiment une présence sur place, et je_x005F_x000D_
+souhaite m'assurer que tout se passe dans les meilleures conditions._x005F_x000D_
+_x005F_x000D_
+Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x005F_x000D_
+pouvez me joindre à l'adresse yessineht@gmail.com, et la destination est_x005F_x000D_
+Kairouan pour ces deux journées. L'accord de mon responsable est encore en_x005F_x000D_
+attente, mais je souhaitais vous transmettre cette demande en avance afin_x005F_x000D_
+d'éviter tout délai de traitement._x005F_x000D_
+_x005F_x000D_
+Si vous avez besoin de quoi que ce soit de ma part — documents_x005F_x000D_
+supplémentaires, détails sur les objectifs de la mission, ou autre —_x005F_x000D_
+n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x005F_x000D_
+plus brefs délais._x005F_x000D_
+_x005F_x000D_
+Merci beaucoup pour votre aide et votre disponibilité !_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Yessine Ht &lt;yessineht@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Demande de recrutement – Poste : Développeur Full Stack/*MailSub*/ 
+ Date: Thu, 21 May 2026 09:45:19 +0100 
+ Madame, Monsieur,_x005F_x000D_
+_x005F_x000D_
+Je me permets de vous adresser la présente afin d'initier une demande de_x005F_x000D_
+recrutement pour le poste de Développeur Full Stack au sein de notre_x005F_x000D_
+département Informatique._x005F_x000D_
+_x005F_x000D_
+**Description du besoin**_x005F_x000D_
+Face à l'accroissement de nos projets de développement, nous avons besoin_x005F_x000D_
+de renforcer notre équipe technique par le recrutement d'un profil_x005F_x000D_
+expérimenté en développement web Full Stack._x005F_x000D_
+_x005F_x000D_
+**Poste**_x005F_x000D_
+Développeur Full Stack_x005F_x000D_
+_x005F_x000D_
+**Documents joints**_x005F_x000D_
+- Fiche de poste : ci-jointe_x005F_x000D_
+- Questionnaire de recrutement : ci-joint_x005F_x000D_
+_x005F_x000D_
+**Présélection des candidats**_x005F_x000D_
+Suite à l'analyse des candidatures reçues, les candidats présélectionnés_x005F_x000D_
+sont les suivants :_x005F_x000D_
+1. Ahmed Ben Salem_x005F_x000D_
+2. Sonia Trabelsi_x005F_x000D_
+3. Karim Mansour_x005F_x000D_
+_x005F_x000D_
+**Entretien(s)**_x005F_x000D_
+- Date d'entretien : 28/05/2026_x005F_x000D_
+- Type d'entretien : Entretien technique + RH_x005F_x000D_
+- Évaluateurs : M. Youssef Chaabane (Responsable technique), Mme Rim_x005F_x000D_
+Bouaziz (RH)_x005F_x000D_
+_x005F_x000D_
+**Résultats**_x005F_x000D_
+- Résultats des questionnaires : ci-joints_x005F_x000D_
+- Résultat de l'entretien : Favorable pour M. Ahmed Ben Salem_x005F_x000D_
+_x005F_x000D_
+**Candidat retenu**_x005F_x000D_
+- Nom du candidat retenu : Ahmed Ben Salem_x005F_x000D_
+- Type de contrat : CDI_x005F_x000D_
+- Date d'embauche : 01/07/2026_x005F_x000D_
+- Seuil de proposition d'embauche : 2 800 TND_x005F_x000D_
+- Proposition finale d'embauche : 3 000 TND_x005F_x000D_
+_x005F_x000D_
+Nous vous prions de bien vouloir procéder à la préparation du contrat et de_x005F_x000D_
+planifier la signature dans les meilleurs délais._x005F_x000D_
+_x005F_x000D_
+Contrat : à établir_x005F_x000D_
+_x005F_x000D_
+Restant à votre disposition pour tout complément d'information,_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+_x005F_x000D_
+Mohamed Khalil_x005F_x000D_
+Responsable Département Informatique_x005F_x000D_
+m.khalil@entreprise.tn | +216 71 000 000</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Yessine Ht &lt;yessineht@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Évaluation de fin de période d'essai – Mme Sonia Trabelsi/*MailSub*/ 
+ Date: Thu, 21 May 2026 09:48:26 +0100 
+ Madame, Monsieur,_x005F_x000D_
+_x005F_x000D_
+Je vous transmets ci-dessous le rapport d'évaluation de fin de période_x005F_x000D_
+d'essai concernant Mme Sonia Trabelsi, intégrée au sein du département_x005F_x000D_
+Ressources Humaines depuis le 01/03/2026._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+I. ÉVALUATION PAR LE SUPÉRIEUR HIÉRARCHIQUE_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+Collaborateur évalué : Mme Sonia Trabelsi_x005F_x000D_
+Responsable évaluateur : M. Youssef Chaabane – Responsable RH_x005F_x000D_
+_x005F_x000D_
+• Connaissance de l'emploi : Bonne maîtrise des procédures internes et des_x005F_x000D_
+outils RH utilisés. S'est rapidement approprié les processus en place._x005F_x000D_
+_x005F_x000D_
+• Productivité (Qualité / Quantité de travail) : Travail soigné et livré_x005F_x000D_
+dans les délais impartis. Volume de tâches traitées conforme aux attentes_x005F_x000D_
+du poste._x005F_x000D_
+_x005F_x000D_
+• Fiabilité : Ponctuelle, rigoureuse et respectueuse de ses engagements._x005F_x000D_
+Aucune absence non justifiée durant la période d'essai._x005F_x000D_
+_x005F_x000D_
+• Collaboration : S'intègre facilement dans les dynamiques d'équipe._x005F_x000D_
+Participe activement aux réunions et contribue aux projets collectifs._x005F_x000D_
+_x005F_x000D_
+• Adaptabilité : A démontré une bonne capacité d'adaptation face aux_x005F_x000D_
+changements de priorités et aux situations imprévues._x005F_x000D_
+_x005F_x000D_
+• Initiative : Fait preuve d'empressement et de proactivité. A proposé_x005F_x000D_
+plusieurs améliorations sur les procédures de suivi des candidatures._x005F_x000D_
+_x005F_x000D_
+• Service à la clientèle / fournisseurs : Interactions professionnelles et_x005F_x000D_
+courtoises avec les partenaires externes et les candidats._x005F_x000D_
+_x005F_x000D_
+• Commentaire général : Mme Trabelsi est une collaboratrice sérieuse et_x005F_x000D_
+investie. Son intégration au sein de l'équipe s'est déroulée de manière_x005F_x000D_
+très satisfaisante._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+II. ÉVALUATION RH_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+• Attitudes et comportements au travail : Comportement exemplaire,_x005F_x000D_
+respectueux des valeurs et du règlement intérieur de l'entreprise._x005F_x000D_
+_x005F_x000D_
+• Motivation et satisfaction personnelle : Se déclare motivée par ses_x005F_x000D_
+missions et exprime un intérêt marqué pour évoluer au sein du département._x005F_x000D_
+_x005F_x000D_
+• Environnement de travail et organisation générale : S'est bien adaptée à_x005F_x000D_
+l'environnement de travail. Espace de travail organisé, gestion du temps_x005F_x000D_
+satisfaisante._x005F_x000D_
+_x005F_x000D_
+• Encadrement et intégration : L'accompagnement réalisé durant la période_x005F_x000D_
+d'essai a été jugé suffisant. La collaboratrice a bénéficié d'un suivi_x005F_x000D_
+régulier par son responsable direct._x005F_x000D_
+_x005F_x000D_
+• Écarts constatés : Légère marge de progression identifiée sur la gestion_x005F_x000D_
+des priorités en période de forte charge. Point à suivre lors du prochain_x005F_x000D_
+entretien annuel._x005F_x000D_
+_x005F_x000D_
+• Relation avec les collègues au sein du département : Excellentes_x005F_x000D_
+relations interpersonnelles. Appréciée par l'ensemble de l'équipe pour son_x005F_x000D_
+esprit d'entraide._x005F_x000D_
+_x005F_x000D_
+• Ambition exprimée : Souhaite à terme prendre en charge le volet formation_x005F_x000D_
+et développement des compétences au sein du département RH._x005F_x000D_
+_x005F_x000D_
+• Proposition d'amélioration : Nous recommandons de lui confier_x005F_x000D_
+progressivement des missions de coordination afin de développer ses_x005F_x000D_
+compétences managériales._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+III. DÉCISION_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+• Décision proposée : Confirmation de la titularisation à l'issue de la_x005F_x000D_
+période d'essai._x005F_x000D_
+• Décision finale : FAVORABLE – Intégration définitive au sein du_x005F_x000D_
+département RH à compter du 01/06/2026._x005F_x000D_
+_x005F_x000D_
+Nous vous prions de bien vouloir prendre note de cette décision et de_x005F_x000D_
+procéder aux formalités administratives nécessaires à la confirmation du_x005F_x000D_
+contrat._x005F_x000D_
+_x005F_x000D_
+Restant à votre disposition pour tout complément d'information,_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+_x005F_x000D_
+Mme Rim Bouaziz_x005F_x000D_
+Chargée des Ressources Humaines_x005F_x000D_
+r.bouaziz@entreprise.tn | +216 71 000 001</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Yessine Ht &lt;yessineht@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Demande d'autorisation d'absence – 27/05/2026/*MailSub*/ 
+ Date: Thu, 21 May 2026 11:27:18 +0100 
+ Madame, Monsieur,_x005F_x000D_
+_x005F_x000D_
+Je me permets de vous adresser la présente afin de solliciter une_x005F_x000D_
+autorisation d'absence pour des raisons personnelles._x005F_x000D_
+_x005F_x000D_
+• Type d'autorisation : Autorisation de sortie exceptionnelle_x005F_x000D_
+• Date de l'absence : 27/05/2026_x005F_x000D_
+• Heure de départ : 10h00_x005F_x000D_
+• Heure de retour : 13h30_x005F_x000D_
+• Nombre d'heures : 3h30_x005F_x000D_
+• Motif de l'absence : Rendez-vous médical spécialisé ne pouvant être_x005F_x000D_
+reporté_x005F_x000D_
+_x005F_x000D_
+Je m'engage à assurer la continuité de mes tâches en amont et à rattraper_x005F_x000D_
+le temps d'absence si cela s'avère nécessaire._x005F_x000D_
+_x005F_x000D_
+Dans l'attente de votre accord, je reste disponible pour tout échange à ce_x005F_x000D_
+sujet._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+_x005F_x000D_
+Ahmed Ben Salem_x005F_x000D_
+Développeur Full Stack – Département Informatique_x005F_x000D_
+a.bensalem@entreprise.tn | +216 55 000 123</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Rayen gargouri &lt;gargourirayen@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Demande d'activation d'une offre Fibre Entreprise/*MailSub*/ 
+ Date: Wed, 3 Jun 2026 00:28:44 +0100 
+ Bonjour,_x000D_
+_x000D_
+Je représente la société TechSolutions et nous souhaitons souscrire à une_x000D_
+offre Fibre Entreprise pour notre nouveau siège situé à Sfax._x000D_
+_x000D_
+Avant de finaliser notre choix, nous aimerions obtenir des informations_x000D_
+concernant les débits disponibles, les délais d'installation, les garanties_x000D_
+de disponibilité du service ainsi que les tarifs applicables aux_x000D_
+entreprises._x000D_
+_x000D_
+Pourriez-vous également nous indiquer les documents nécessaires à la_x000D_
+souscription et les coordonnées d'un conseiller commercial pouvant nous_x000D_
+accompagner dans cette démarche ?_x000D_
+_x000D_
+Je vous remercie pour votre aide et reste dans l'attente de votre retour._x000D_
 _x000D_
 Cordialement,_x000D_
-yessine haj taieb</t>
+_x000D_
+Mohamed Rayen GARGOURI_x000D_
+Responsable Administratif</t>
+  </si>
+  <si>
+    <t>From: /*MailSender*/Rayen gargouri &lt;gargourirayen@gmail.com&gt;/*MailSender*/ 
+ Subject: /*MailSub*/Réclamation concernant des coupures répétées de la connexion Internet/*MailSub*/ 
+ Date: Wed, 3 Jun 2026 00:30:12 +0100 
+ Bonjour,_x000D_
+_x000D_
+Je me permets de vous contacter afin de signaler un problème récurrent_x000D_
+affectant ma connexion Internet Orange._x000D_
+_x000D_
+Depuis environ une semaine, je constate plusieurs coupures quotidiennes qui_x000D_
+interrompent régulièrement mes activités professionnelles en télétravail._x000D_
+Malgré plusieurs redémarrages du routeur, le problème persiste et la_x000D_
+qualité de la connexion reste très instable._x000D_
+_x000D_
+Cette situation me cause un réel préjudice et je souhaiterais qu'une_x000D_
+vérification technique soit effectuée dans les meilleurs délais afin_x000D_
+d'identifier l'origine du dysfonctionnement._x000D_
+_x000D_
+Je vous remercie de bien vouloir prendre en compte ma réclamation et de me_x000D_
+tenir informé des actions entreprises._x000D_
+_x000D_
+Cordialement,_x000D_
+_x000D_
+Mohamed Rayen GARGOURI_x000D_
+Client_x000D_
+Numéro de ligne : 52 123 456</t>
   </si>
   <si>
     <t>Doctor_Note_with_Signature.pdf</t>
@@ -456,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -475,7 +715,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -483,10 +723,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -494,10 +734,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -505,18 +745,58 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
